--- a/public/file/Trax Book Omni Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Omni Corporate Shipment Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F0399B-4DBA-47BC-9CA5-5DF6D4276299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="8964"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -132,12 +133,15 @@
   </si>
   <si>
     <t>Return Address Id</t>
+  </si>
+  <si>
+    <t>Parcel Value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -483,8 +487,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AJ1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -520,7 +524,7 @@
     <col min="36" max="36" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -628,6 +632,9 @@
       </c>
       <c r="AJ1" t="s">
         <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Omni Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Omni Corporate Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F0399B-4DBA-47BC-9CA5-5DF6D4276299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487BA132-62F2-422E-BF00-EEEDFC48E0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -522,6 +522,7 @@
     <col min="30" max="34" width="24.5546875" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="15.88671875" customWidth="1"/>
     <col min="36" max="36" width="15.6640625" customWidth="1"/>
+    <col min="37" max="37" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.3">
@@ -633,7 +634,7 @@
       <c r="AJ1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
     </row>

--- a/public/file/Trax Book Omni Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Omni Corporate Shipment Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487BA132-62F2-422E-BF00-EEEDFC48E0BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -136,12 +135,18 @@
   </si>
   <si>
     <t>Parcel Value</t>
+  </si>
+  <si>
+    <t>Consignee Address Latitude</t>
+  </si>
+  <si>
+    <t>Consignee Address Longitude</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -487,8 +492,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -500,32 +505,32 @@
     <col min="7" max="7" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.33203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.21875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="26" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.88671875" style="1"/>
-    <col min="30" max="34" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.88671875" customWidth="1"/>
-    <col min="36" max="36" width="15.6640625" customWidth="1"/>
-    <col min="37" max="37" width="8.88671875" style="1"/>
+    <col min="11" max="13" width="21.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.21875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="29.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.88671875" style="1"/>
+    <col min="32" max="36" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.88671875" customWidth="1"/>
+    <col min="38" max="38" width="15.6640625" customWidth="1"/>
+    <col min="39" max="39" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -557,84 +562,90 @@
         <v>2</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>36</v>
       </c>
     </row>

--- a/public/file/Trax Book Omni Corporate Shipment Template.xlsx
+++ b/public/file/Trax Book Omni Corporate Shipment Template.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t>Consignee Address Longitude</t>
+  </si>
+  <si>
+    <t>Retail Pickup Store ID</t>
+  </si>
+  <si>
+    <t>Retail Deliver Store ID</t>
   </si>
 </sst>
 </file>
@@ -493,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -530,7 +536,7 @@
     <col min="39" max="39" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -647,6 +653,12 @@
       </c>
       <c r="AM1" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
